--- a/Baja_SAE_Controls_Gantt.xlsx
+++ b/Baja_SAE_Controls_Gantt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexmiller/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB1571BD-393E-7344-AAC8-7CA4B8C36F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0FCC49-58C5-E54C-94F2-5BF7C9EA5D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="200">
   <si>
     <t>Baja SAE – Controls  |  Capstone Project Gantt Chart</t>
   </si>
@@ -659,6 +659,9 @@
   </si>
   <si>
     <t>Part Selection Deadline</t>
+  </si>
+  <si>
+    <t>AdI04</t>
   </si>
 </sst>
 </file>
@@ -6833,8 +6836,12 @@
       </c>
     </row>
     <row r="42" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="26"/>
-      <c r="B42" s="27"/>
+      <c r="A42" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>197</v>
+      </c>
       <c r="C42" s="28" t="s">
         <v>198</v>
       </c>
@@ -6994,7 +7001,7 @@
     </row>
     <row r="43" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="26" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B43" s="27" t="s">
         <v>197</v>
